--- a/Shiny/Datos limpios/pricing_diario_historico.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_historico.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3822"/>
+  <dimension ref="A1:H3847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98521,10 +98521,10 @@
         <v>5645.639999999999</v>
       </c>
       <c r="G3775">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="H3775">
-        <v>410059.26</v>
+        <v>409918.58</v>
       </c>
     </row>
     <row r="3776">
@@ -98729,10 +98729,10 @@
         <v>3401.69</v>
       </c>
       <c r="G3783">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="H3783">
-        <v>438744.4300000001</v>
+        <v>438710.51</v>
       </c>
     </row>
     <row r="3784">
@@ -98853,7 +98853,7 @@
         <v>72983.32000000001</v>
       </c>
       <c r="E3788">
-        <v>481877.8100000001</v>
+        <v>480607.55</v>
       </c>
       <c r="F3788">
         <v>3468.49</v>
@@ -98862,7 +98862,7 @@
         <v>100670.96</v>
       </c>
       <c r="H3788">
-        <v>665943.84</v>
+        <v>664673.58</v>
       </c>
     </row>
     <row r="3789">
@@ -98885,10 +98885,10 @@
         <v>563.99</v>
       </c>
       <c r="G3789">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="H3789">
-        <v>1706993.91</v>
+        <v>1706806.18</v>
       </c>
     </row>
     <row r="3790">
@@ -98905,16 +98905,16 @@
         <v>206389.3</v>
       </c>
       <c r="E3790">
-        <v>1574424.4</v>
+        <v>1574405.94</v>
       </c>
       <c r="F3790">
         <v>1872.14</v>
       </c>
       <c r="G3790">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="H3790">
-        <v>2042044.69</v>
+        <v>2041026.23</v>
       </c>
     </row>
     <row r="3791">
@@ -98931,7 +98931,7 @@
         <v>152926.75</v>
       </c>
       <c r="E3791">
-        <v>837417.1100000001</v>
+        <v>837359.4</v>
       </c>
       <c r="F3791">
         <v>5454.65</v>
@@ -98940,7 +98940,7 @@
         <v>106359.36</v>
       </c>
       <c r="H3791">
-        <v>1144108.5</v>
+        <v>1144050.79</v>
       </c>
     </row>
     <row r="3792">
@@ -99087,16 +99087,16 @@
         <v>70085.70999999999</v>
       </c>
       <c r="E3797">
-        <v>380373.22</v>
+        <v>380369.38</v>
       </c>
       <c r="F3797">
         <v>11864.14</v>
       </c>
       <c r="G3797">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="H3797">
-        <v>556041.9</v>
+        <v>555916.5700000001</v>
       </c>
     </row>
     <row r="3798">
@@ -99113,7 +99113,7 @@
         <v>92329.42</v>
       </c>
       <c r="E3798">
-        <v>370912.65</v>
+        <v>370765.3</v>
       </c>
       <c r="F3798">
         <v>1132.62</v>
@@ -99122,7 +99122,7 @@
         <v>69660.97</v>
       </c>
       <c r="H3798">
-        <v>557229.26</v>
+        <v>557081.91</v>
       </c>
     </row>
     <row r="3799">
@@ -99139,16 +99139,16 @@
         <v>90230.02000000002</v>
       </c>
       <c r="E3799">
-        <v>423023.69</v>
+        <v>423024.43</v>
       </c>
       <c r="F3799">
         <v>12823.31</v>
       </c>
       <c r="G3799">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="H3799">
-        <v>660036.8800000001</v>
+        <v>659747.53</v>
       </c>
     </row>
     <row r="3800">
@@ -99217,7 +99217,7 @@
         <v>97668.79000000001</v>
       </c>
       <c r="E3802">
-        <v>227120.04</v>
+        <v>227000.04</v>
       </c>
       <c r="F3802">
         <v>1361.07</v>
@@ -99226,7 +99226,7 @@
         <v>83410.52</v>
       </c>
       <c r="H3802">
-        <v>427881.6800000001</v>
+        <v>427761.6800000001</v>
       </c>
     </row>
     <row r="3803">
@@ -99249,10 +99249,10 @@
         <v>994.22</v>
       </c>
       <c r="G3803">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="H3803">
-        <v>420817.7</v>
+        <v>420662.43</v>
       </c>
     </row>
     <row r="3804">
@@ -99405,10 +99405,10 @@
         <v>901.3099999999999</v>
       </c>
       <c r="G3809">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="H3809">
-        <v>324046.59</v>
+        <v>323750.03</v>
       </c>
     </row>
     <row r="3810">
@@ -99506,13 +99506,13 @@
         <v>106043.07</v>
       </c>
       <c r="F3813">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="G3813">
         <v>107090.62</v>
       </c>
       <c r="H3813">
-        <v>408688.26</v>
+        <v>407688.26</v>
       </c>
     </row>
     <row r="3814">
@@ -99728,25 +99728,675 @@
         <v>45957</v>
       </c>
       <c r="B3822">
-        <v>7950</v>
+        <v>19388.34</v>
       </c>
       <c r="C3822">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="D3822">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="E3822">
-        <v>2677.84</v>
+        <v>56853.16</v>
       </c>
       <c r="F3822">
-        <v>0</v>
+        <v>1289.08</v>
       </c>
       <c r="G3822">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="H3822">
-        <v>14047.84</v>
+        <v>211136.45</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B3823">
+        <v>18221.26</v>
+      </c>
+      <c r="C3823">
+        <v>11008.73</v>
+      </c>
+      <c r="D3823">
+        <v>117118.26</v>
+      </c>
+      <c r="E3823">
+        <v>118743.84</v>
+      </c>
+      <c r="F3823">
+        <v>1556.12</v>
+      </c>
+      <c r="G3823">
+        <v>102356.76</v>
+      </c>
+      <c r="H3823">
+        <v>369004.97</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B3824">
+        <v>11773</v>
+      </c>
+      <c r="C3824">
+        <v>10770.94</v>
+      </c>
+      <c r="D3824">
+        <v>95470.38</v>
+      </c>
+      <c r="E3824">
+        <v>58551.82</v>
+      </c>
+      <c r="F3824">
+        <v>1664.4</v>
+      </c>
+      <c r="G3824">
+        <v>62442.2</v>
+      </c>
+      <c r="H3824">
+        <v>240672.74</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B3825">
+        <v>21536.23</v>
+      </c>
+      <c r="C3825">
+        <v>11518.56</v>
+      </c>
+      <c r="D3825">
+        <v>130203.01</v>
+      </c>
+      <c r="E3825">
+        <v>55796.11</v>
+      </c>
+      <c r="F3825">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="G3825">
+        <v>92197.7</v>
+      </c>
+      <c r="H3825">
+        <v>312143.67</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B3826">
+        <v>31360</v>
+      </c>
+      <c r="C3826">
+        <v>8032.99</v>
+      </c>
+      <c r="D3826">
+        <v>146743.22</v>
+      </c>
+      <c r="E3826">
+        <v>48408.11</v>
+      </c>
+      <c r="F3826">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="G3826">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="H3826">
+        <v>332766.88</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B3827">
+        <v>0</v>
+      </c>
+      <c r="C3827">
+        <v>0</v>
+      </c>
+      <c r="D3827">
+        <v>159.87</v>
+      </c>
+      <c r="E3827">
+        <v>2215.14</v>
+      </c>
+      <c r="F3827">
+        <v>0</v>
+      </c>
+      <c r="G3827">
+        <v>1597.81</v>
+      </c>
+      <c r="H3827">
+        <v>3972.82</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B3828">
+        <v>0</v>
+      </c>
+      <c r="C3828">
+        <v>0</v>
+      </c>
+      <c r="D3828">
+        <v>0</v>
+      </c>
+      <c r="E3828">
+        <v>13081.43</v>
+      </c>
+      <c r="F3828">
+        <v>0</v>
+      </c>
+      <c r="G3828">
+        <v>0</v>
+      </c>
+      <c r="H3828">
+        <v>13081.43</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B3829">
+        <v>26455.8</v>
+      </c>
+      <c r="C3829">
+        <v>8996.65</v>
+      </c>
+      <c r="D3829">
+        <v>137256.09</v>
+      </c>
+      <c r="E3829">
+        <v>81738.89999999999</v>
+      </c>
+      <c r="F3829">
+        <v>2699.28</v>
+      </c>
+      <c r="G3829">
+        <v>99453.11</v>
+      </c>
+      <c r="H3829">
+        <v>356599.83</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B3830">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="C3830">
+        <v>31218.63</v>
+      </c>
+      <c r="D3830">
+        <v>100755.44</v>
+      </c>
+      <c r="E3830">
+        <v>107688.57</v>
+      </c>
+      <c r="F3830">
+        <v>1710.15</v>
+      </c>
+      <c r="G3830">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="H3830">
+        <v>360333.8700000001</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B3831">
+        <v>20673.65</v>
+      </c>
+      <c r="C3831">
+        <v>22130.88</v>
+      </c>
+      <c r="D3831">
+        <v>295755.66</v>
+      </c>
+      <c r="E3831">
+        <v>42870.54</v>
+      </c>
+      <c r="F3831">
+        <v>4628.26</v>
+      </c>
+      <c r="G3831">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="H3831">
+        <v>481351.6900000001</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B3832">
+        <v>12292.76</v>
+      </c>
+      <c r="C3832">
+        <v>-5764.84</v>
+      </c>
+      <c r="D3832">
+        <v>212826.47</v>
+      </c>
+      <c r="E3832">
+        <v>111236.27</v>
+      </c>
+      <c r="F3832">
+        <v>1946.28</v>
+      </c>
+      <c r="G3832">
+        <v>71152.63</v>
+      </c>
+      <c r="H3832">
+        <v>403689.57</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B3833">
+        <v>23785.06</v>
+      </c>
+      <c r="C3833">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="D3833">
+        <v>127060.58</v>
+      </c>
+      <c r="E3833">
+        <v>127863.62</v>
+      </c>
+      <c r="F3833">
+        <v>2209.08</v>
+      </c>
+      <c r="G3833">
+        <v>61774.31</v>
+      </c>
+      <c r="H3833">
+        <v>352006.43</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B3834">
+        <v>0</v>
+      </c>
+      <c r="C3834">
+        <v>15</v>
+      </c>
+      <c r="D3834">
+        <v>516.72</v>
+      </c>
+      <c r="E3834">
+        <v>1378.62</v>
+      </c>
+      <c r="F3834">
+        <v>0</v>
+      </c>
+      <c r="G3834">
+        <v>254.2</v>
+      </c>
+      <c r="H3834">
+        <v>2164.54</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B3835">
+        <v>0</v>
+      </c>
+      <c r="C3835">
+        <v>0</v>
+      </c>
+      <c r="D3835">
+        <v>35</v>
+      </c>
+      <c r="E3835">
+        <v>500</v>
+      </c>
+      <c r="F3835">
+        <v>0</v>
+      </c>
+      <c r="G3835">
+        <v>0</v>
+      </c>
+      <c r="H3835">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B3836">
+        <v>14799.99</v>
+      </c>
+      <c r="C3836">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="D3836">
+        <v>147347.01</v>
+      </c>
+      <c r="E3836">
+        <v>51602.62</v>
+      </c>
+      <c r="F3836">
+        <v>2021.14</v>
+      </c>
+      <c r="G3836">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="H3836">
+        <v>316742.97</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B3837">
+        <v>22060.6</v>
+      </c>
+      <c r="C3837">
+        <v>15913.23</v>
+      </c>
+      <c r="D3837">
+        <v>187223.45</v>
+      </c>
+      <c r="E3837">
+        <v>68845.47</v>
+      </c>
+      <c r="F3837">
+        <v>1437.55</v>
+      </c>
+      <c r="G3837">
+        <v>92712.08</v>
+      </c>
+      <c r="H3837">
+        <v>388192.38</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B3838">
+        <v>10481.56</v>
+      </c>
+      <c r="C3838">
+        <v>11562.86</v>
+      </c>
+      <c r="D3838">
+        <v>122982.8</v>
+      </c>
+      <c r="E3838">
+        <v>85335.42000000001</v>
+      </c>
+      <c r="F3838">
+        <v>1078.46</v>
+      </c>
+      <c r="G3838">
+        <v>109947.54</v>
+      </c>
+      <c r="H3838">
+        <v>341388.64</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B3839">
+        <v>15739.25</v>
+      </c>
+      <c r="C3839">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="D3839">
+        <v>195224.96</v>
+      </c>
+      <c r="E3839">
+        <v>75975.76999999999</v>
+      </c>
+      <c r="F3839">
+        <v>1881.48</v>
+      </c>
+      <c r="G3839">
+        <v>145746.27</v>
+      </c>
+      <c r="H3839">
+        <v>444560.96</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B3840">
+        <v>14622.57</v>
+      </c>
+      <c r="C3840">
+        <v>10007.08</v>
+      </c>
+      <c r="D3840">
+        <v>359640.37</v>
+      </c>
+      <c r="E3840">
+        <v>51099.35</v>
+      </c>
+      <c r="F3840">
+        <v>1177.15</v>
+      </c>
+      <c r="G3840">
+        <v>159314.17</v>
+      </c>
+      <c r="H3840">
+        <v>595860.6900000001</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B3841">
+        <v>0</v>
+      </c>
+      <c r="C3841">
+        <v>0</v>
+      </c>
+      <c r="D3841">
+        <v>1776.47</v>
+      </c>
+      <c r="E3841">
+        <v>180</v>
+      </c>
+      <c r="F3841">
+        <v>145</v>
+      </c>
+      <c r="G3841">
+        <v>720</v>
+      </c>
+      <c r="H3841">
+        <v>2821.47</v>
+      </c>
+    </row>
+    <row r="3842">
+      <c r="A3842" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B3842">
+        <v>0</v>
+      </c>
+      <c r="C3842">
+        <v>800.28</v>
+      </c>
+      <c r="D3842">
+        <v>0</v>
+      </c>
+      <c r="E3842">
+        <v>500</v>
+      </c>
+      <c r="F3842">
+        <v>0</v>
+      </c>
+      <c r="G3842">
+        <v>0</v>
+      </c>
+      <c r="H3842">
+        <v>1300.28</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B3843">
+        <v>31748.74</v>
+      </c>
+      <c r="C3843">
+        <v>8849.66</v>
+      </c>
+      <c r="D3843">
+        <v>113945.08</v>
+      </c>
+      <c r="E3843">
+        <v>74008.22</v>
+      </c>
+      <c r="F3843">
+        <v>743.95</v>
+      </c>
+      <c r="G3843">
+        <v>113416.33</v>
+      </c>
+      <c r="H3843">
+        <v>342711.98</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B3844">
+        <v>27423.37</v>
+      </c>
+      <c r="C3844">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="D3844">
+        <v>80879.83</v>
+      </c>
+      <c r="E3844">
+        <v>102518.02</v>
+      </c>
+      <c r="F3844">
+        <v>480</v>
+      </c>
+      <c r="G3844">
+        <v>116519.79</v>
+      </c>
+      <c r="H3844">
+        <v>334487.11</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B3845">
+        <v>27056</v>
+      </c>
+      <c r="C3845">
+        <v>15932.94</v>
+      </c>
+      <c r="D3845">
+        <v>113818.39</v>
+      </c>
+      <c r="E3845">
+        <v>97366.82999999999</v>
+      </c>
+      <c r="F3845">
+        <v>462.46</v>
+      </c>
+      <c r="G3845">
+        <v>136266.54</v>
+      </c>
+      <c r="H3845">
+        <v>390903.16</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B3846">
+        <v>29415.74</v>
+      </c>
+      <c r="C3846">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="D3846">
+        <v>68768.36</v>
+      </c>
+      <c r="E3846">
+        <v>66451.56</v>
+      </c>
+      <c r="F3846">
+        <v>2027.73</v>
+      </c>
+      <c r="G3846">
+        <v>100749.12</v>
+      </c>
+      <c r="H3846">
+        <v>277102.79</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B3847">
+        <v>10210</v>
+      </c>
+      <c r="C3847">
+        <v>2256.3</v>
+      </c>
+      <c r="D3847">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="E3847">
+        <v>11084.31</v>
+      </c>
+      <c r="F3847">
+        <v>0</v>
+      </c>
+      <c r="G3847">
+        <v>20391.37</v>
+      </c>
+      <c r="H3847">
+        <v>50991.29</v>
       </c>
     </row>
   </sheetData>
